--- a/output/第10期計画_年報月報の受領点検.xlsx
+++ b/output/第10期計画_年報月報の受領点検.xlsx
@@ -754,12 +754,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>画像を文字認識したPDFであり、読み取りに誤りがあります（「1,102」を「1021」と読むなど）。第1号被保険者数と受給者数は内部の合計と照合できました。</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>要目視照合</t>
+          <t>文字認識には誤りがあったため、画像を目視で確認して値を確定しました。行計・列計・合計との整合をすべて確認済みです。4月報の前月末が令和7年度の年報の年度末と一致し、年報と月報は接続しています。</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3474,14 +3474,14 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>月報は令和8年4〜7月の4か月です。スキャンしたPDFであり、文字認識による読み取りには誤りがあるため、計画本文に用いる前に原本との目視の照合を要します。</t>
+          <t>月報は令和8年4〜7月の4か月です。スキャンしたPDFのため文字認識では誤りが生じましたが、画像を目視で確認し、行計・列計・合計との整合をすべて確認したうえで値を確定しました。PDFのままで支障ありません。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>【1　月報から読み取った値】</t>
+          <t>【1　月報の値（画像の目視により確定）】</t>
         </is>
       </c>
     </row>
@@ -3498,22 +3498,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>令和8年4月</t>
+          <t>令和8年4月分</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>令和8年5月</t>
+          <t>令和8年5月分</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>令和8年6月</t>
+          <t>令和8年6月分</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>令和8年7月</t>
+          <t>令和8年7月分</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -3528,24 +3528,24 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者数　65歳以上75歳未満</t>
+          <t>第1号被保険者数　前月末</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3592</v>
+        <v>9090</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>3593</v>
+        <v>9088</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3578</v>
+        <v>9087</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3560</v>
+        <v>9067</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>4月3,592人から7月3,560人へ減少。</t>
+          <t>4月報の前月末9,090人は令和7年度の年報の年度末と一致します。年齢区分別（3,607／3,493／1,990人）も完全に一致し、年報と月報は接続しています。</t>
         </is>
       </c>
     </row>
@@ -3555,24 +3555,24 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者数　75歳以上85歳未満</t>
+          <t>第1号被保険者数　当月中増</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3493</v>
+        <v>35</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3494</v>
+        <v>40</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3497</v>
+        <v>32</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3490</v>
+        <v>28</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>ほぼ横ばい。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3582,24 +3582,24 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者数　85歳以上</t>
+          <t>第1号被保険者数　当月中減</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2003</v>
+        <v>37</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1999</v>
+        <v>42</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1993</v>
+        <v>51</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>2003</v>
+        <v>42</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>1,993〜2,003人で推移。</t>
+          <t>6月は51人と多く、当月末が18人減少しました。</t>
         </is>
       </c>
     </row>
@@ -3607,9 +3607,9 @@
       <c r="A9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>第1号被保険者数　計（月末）</t>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>第1号被保険者数　当月末</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>9,088人から9,053人へ35人減。年度末9,090人からの推移と整合します。</t>
+          <t>9,088人から9,053人へ35人減。各月とも「前月末＋当月中増−当月中減＝当月末」が成立します。</t>
         </is>
       </c>
     </row>
@@ -3636,24 +3636,24 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>居宅（介護予防）サービス受給者数　合計</t>
+          <t>第1号被保険者数　65歳以上75歳未満</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1082</v>
+        <v>3592</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>1108</v>
+        <v>3593</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>1126</v>
+        <v>3578</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1127</v>
+        <v>3560</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>1,082人から1,127人へ増加。令和7年度の月平均1,079人を上回ります。</t>
+          <t>3,592人から3,560人へ32人減。</t>
         </is>
       </c>
     </row>
@@ -3663,26 +3663,24 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス受給者数　合計</t>
+          <t>第1号被保険者数　75歳以上85歳未満</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>316</v>
+        <v>3493</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>317</v>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>要照合</t>
-        </is>
+        <v>3494</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>3497</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>310</v>
+        <v>3490</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>6月は読み取れませんでした。目視の照合を要します。</t>
+          <t>3,493人から3,490人へ。ほぼ横ばい。</t>
         </is>
       </c>
     </row>
@@ -3692,326 +3690,740 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>施設介護サービス受給者数　合計</t>
+          <t>第1号被保険者数　85歳以上</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>1993</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>1,993〜2,003人で推移。年齢区分別の計は各月とも当月末と一致します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>居宅サービス受給者数　総数</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>1082</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>1108</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>1127</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>1,082人から1,127人へ増加。令和7年度の月平均1,079人を4月以降すべて上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>地域密着型サービス受給者数　総数</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>316</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>317</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>316</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>310</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>316〜317人で推移し、7月に310人へ。令和7年度の月平均318人とほぼ同水準です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス受給者数　介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
         <v>136</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D15" s="11" t="n">
         <v>139</v>
       </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>要照合</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="E15" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="F15" s="11" t="n">
         <v>141</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>同上。4月136人・5月139人・7月141人。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>136人から141人へ増加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス受給者数　介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>136〜142人で推移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス受給者数　介護療養型医療施設</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>4か月とも0人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス受給者数　介護医療院</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>4・5月は6人、6・7月は3人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>施設サービス受給者数　総数</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>278</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>285</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>284</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>280</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>278人から280人。令和7年度の月平均277人とほぼ同水準です。居宅が増える一方で施設は横ばいという令和6→7年度の傾向が続いています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>【2　目視の確認により判明した接続のずれ（3件）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>受託者の考え</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>令和8年6月</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>前月末の被保険者数</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>6月報の前月末9,087人に対し、5月報の当月末は9,086人で1人多い。</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>遡及訂正によるものと考えられます。各月の内部計算は成立しており、年度末には整合するものと解しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>令和8年7月</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>前月末の被保険者数</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>7月報の前月末9,067人に対し、6月報の当月末は9,068人で1人少ない。</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>遡及訂正によるものと考えられます。各月の内部計算は成立しており、年度末には整合するものと解しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>令和8年6月</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>施設サービス受給者数の総数</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>施設種別の合計285人に対し、総数は284人で1人少ない。同一月に2施設を利用した者が総数では1人と数えられたものと解される。4月・5月・7月は施設種別の合計と総数が一致する。</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>国の様式の性格によるものであり、誤りではないと解しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>【3　確定の方法】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>文字認識による読み取り</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>PDFに埋め込まれた文字情報を機械的に読み取りました。読み取り順が乱れており、「1,102」を「1021」と読む、施設サービスの総数を施設種別の1行と取り違えるなどの誤りがありました。</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>採用しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>画像の目視による確認</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>各ページを画像として表示し、様式1（第1号被保険者数）と様式1の6（受給者数）の全欄を目視で確認しました。帳票が傾いてスキャンされている月（6月）は、該当箇所を拡大して1マスずつ確認しました。</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>採用</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>整合の確認</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>①前月末＋当月中増−当月中減＝当月末、②年齢区分別の計＝当月末、③要支援・要介護の各計＝合計、④第1号＋第2号＝総数、⑤施設種別の合計＝総数、の5つをすべての月について確認しました。</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="21" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>①〜④は全月成立
+⑤は6月のみ1人差</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>年報との接続の確認</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>4月報の前月末（総数及び年齢区分別）が令和7年度の年報の年度末と一致することを確認しました。</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>【2　月報に含まれない様式】</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>様式</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>何が得られないか</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="23" t="n">
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>様式1の5（要介護認定者数）</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>令和8年度の認定者数の月次の推移。代表KPI①要介護認定率・④重度要介護認定率の令和8年度の値。</t>
         </is>
       </c>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>見える化B系列により推定します。打合せでご了承いただいた方針によります。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="23" t="n">
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>様式3（保険料収納状況）</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>令和8年度の保険料の調定額・収納額。</t>
         </is>
       </c>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D37" s="21" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>年度途中のため、令和8年度の収納率は年度末まで確定しません。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="23" t="n">
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>様式4（介護保険特別会計経理状況）</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>令和8年度の決算額と介護給付費準備基金の残高。</t>
         </is>
       </c>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>令和8年度は年度途中であり、決算は本業務の期間中に確定しません。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>【3　なお必要な資料】</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>なぜ必要か</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="64" customHeight="1">
-      <c r="A22" s="23" t="n">
+      <c r="G41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>年報（令和7年度）の様式4・経理状況</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>令和7年度は様式4・様式4の2・様式4の3・経理状況が全項目0で未入力です。第10期の保険料算定には令和7年度末の介護給付費準備基金の残高が必要です。決算の整理が済み次第ご提供をお願いします。</t>
         </is>
       </c>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="23" t="n">
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>月報のExcel形式の原本</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>月報はスキャンPDFであり、文字認識に誤りがあります（「1,102」を「1021」と読むなど）。年報と同じExcel形式でご提供いただければ、誤りなく取り込むことができます。困難な場合は、当方で読み取った値（本シート1）をご確認いただく方法でも差し支えありません。</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="23" t="n">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月以降の月報</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の推移の把握に用います。PDFで差し支えありません。本シート3の方法により確定できます。毎月のご提供をお願いします。</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>令和8年8月以降の月報</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の推移の把握に用います。毎月のご提供をお願いします。</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>第9期の3か年の基準額の確認</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度の標準月額保険料は6,400円です。令和7年度の欄は未入力でした。第9期（令和6〜8年度）を通じて6,400円で相違ないかご確認ください。</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="23" t="n">
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>第9期の3か年の基準額の確認</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度の標準月額保険料は6,400円です。令和7年度の欄は未入力でした。第9期（令和6〜8年度）を通じて6,400円で相違ないかご確認ください。</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="23" t="n">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業・任意事業の実績</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>年報の様式4では地域支援事業費が科目単位でしか分かりません。事業ごとの相談件数・実人数・会議回数は含まれません。資料提供依頼No.13の03シートのご記入が必要です。</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>包括的支援事業・任意事業の実績</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>年報の様式4では地域支援事業費が科目単位でしか分かりません。事業ごとの相談件数・実人数・会議回数は含まれません。資料提供依頼No.13の03シートのご記入が必要です。</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>19施策ごとの事業量・対象実人数・決算額</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>年報は保険給付と会計の報告であり、第9期計画 第5章の19施策の実績は含まれません。資料提供依頼No.13の02シートのご記入が必要です。</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>19施策ごとの事業量・対象実人数・決算額</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>年報は保険給付と会計の報告であり、第9期計画 第5章の19施策の実績は含まれません。資料提供依頼No.13の02シートのご記入が必要です。</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="76" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="76" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>注1）本受領により、資料提供依頼No.13の05シート（決算の状況）は令和6年度分が埋まりました。令和7年度分は様式4が未入力です。
 注2）02シート（19施策の実績）と03シートの包括的支援事業・任意事業は手つかずのままです。この2つは公表資料でも年報でも代替できず、第9期のプロセス評価を止めています。
-注3）月報から読み取った値は、内部の合計との整合を確認できたものに限って収めています。「要照合」は読み取りに誤りがあり値を確定できなかったものです。</t>
+注3）月報の値は画像の目視により確定しており、確定できなかった欄はありません。接続のずれ3件（本シート2）は、いずれも各月の内部計算が成立しており、値そのものの誤りではないと解しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="C18:F18"/>
+  <mergeCells count="23">
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D24:F24"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="C45:E45"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_年報月報の受領点検.xlsx
+++ b/output/第10期計画_年報月報の受領点検.xlsx
@@ -2707,7 +2707,7 @@
       <c r="D46" s="6" t="inlineStr"/>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>231,689,018円。第10期の保険料算定における取崩額の設定に直結する。これまで公表資料では得られず、素案 第6章第6節を［要確認］としていた項目である。</t>
+          <t>231,689,018円。第10期の保険料算定における取崩額の設定に直結する。これまで公表資料では得られず、素案 第6章第6節を［要確認］としていた項目である。令和6年度決算書の財産に関する調書と一致する。同調書により前年度末（第8期末）残高231,456,821円も判明した。</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,8 @@
     <row r="49" ht="88" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>注1）令和7年度の様式4・様式4の2・様式4の3及び経理状況は全項目が0であり、未入力と解されます。決算額と基金の令和7年度末残高は本受領では得られません。第10期の保険料算定には令和7年度末の基金残高が必要です（04シート）。
+          <t>注0）令和6年度分は、令和8年8月28日に受領した令和6年度決算書（介護保険特別会計）と対照し、歳入10項目・歳出12項目のすべてで一致することを確認しました（令和6年度決算書の受領点検 03シート）。
+注1）令和7年度の様式4・様式4の2・様式4の3及び経理状況は全項目が0であり、未入力と解されます。決算額と基金の令和7年度末残高は本受領では得られません。第10期の保険料算定には令和7年度末の基金残高が必要です（04シート）。
 注2）介護給付費準備基金保有額231,689,018円は令和6年度末の値です。令和7年度に精算後残額124,207,196円が積み立てられていれば、令和7年度末は3億5千万円台となる可能性がありますが、推測であり確認を要します。
 注3）保険料収納率の実績（99.8％台）は、計画作成支援ツールの予定収納率99％を上回ります。第10期の算定にどちらを用いるかご確認をお願いします。</t>
         </is>
